--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0003T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.18968390623361</v>
+        <v>11.73082363476296</v>
       </c>
       <c r="D2" t="n">
-        <v>77.16771006727828</v>
+        <v>12.53975288593272</v>
       </c>
       <c r="E2" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F2" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>46.66817023221887</v>
+        <v>7.583577662735567</v>
       </c>
       <c r="D3" t="n">
-        <v>47.70945317593955</v>
+        <v>7.752786141090177</v>
       </c>
       <c r="E3" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F3" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.42298567374695</v>
+        <v>5.26873517198388</v>
       </c>
       <c r="D4" t="n">
-        <v>33.20391543176798</v>
+        <v>5.395636257662297</v>
       </c>
       <c r="E4" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F4" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>49.66135318333563</v>
+        <v>8.06996989229204</v>
       </c>
       <c r="D5" t="n">
-        <v>49.09175083453431</v>
+        <v>7.977409510611825</v>
       </c>
       <c r="E5" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F5" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.41042887656828</v>
+        <v>7.379194692442345</v>
       </c>
       <c r="D6" t="n">
-        <v>49.79997436072787</v>
+        <v>8.092495833618278</v>
       </c>
       <c r="E6" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F6" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>20.11218536111877</v>
+        <v>3.2682301211818</v>
       </c>
       <c r="D7" t="n">
-        <v>21.10094784600919</v>
+        <v>3.428904024976493</v>
       </c>
       <c r="E7" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F7" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.80981140406655</v>
+        <v>3.381594353160815</v>
       </c>
       <c r="D8" t="n">
-        <v>20.33528315192332</v>
+        <v>3.30448351218754</v>
       </c>
       <c r="E8" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F8" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.82577812716962</v>
+        <v>6.146688945665064</v>
       </c>
       <c r="D9" t="n">
-        <v>32.46921619010844</v>
+        <v>5.276247630892621</v>
       </c>
       <c r="E9" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F9" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>13.86115453121678</v>
+        <v>2.252437611322728</v>
       </c>
       <c r="D10" t="n">
-        <v>12.49451268446362</v>
+        <v>2.030358311225338</v>
       </c>
       <c r="E10" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F10" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.97881905156709</v>
+        <v>3.084058095879652</v>
       </c>
       <c r="D11" t="n">
-        <v>16.21202373014551</v>
+        <v>2.634453856148645</v>
       </c>
       <c r="E11" t="n">
-        <v>17.2551721891036</v>
+        <v>2.803965480729335</v>
       </c>
       <c r="F11" t="n">
-        <v>19.04055988942772</v>
+        <v>3.094090982032004</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
